--- a/assets/master-template.xlsx
+++ b/assets/master-template.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Income Statement" sheetId="5" r:id="rId3"/>
     <sheet name="D-110 Flow-through K-1s" sheetId="41" state="hidden" r:id="rId4"/>
     <sheet name="Balance Sheet" sheetId="7" r:id="rId5"/>
+    <sheet name="Retained Earnings" sheetId="60" r:id="rIdRE"/>
     <sheet name="Dividends" sheetId="35" r:id="rId6"/>
     <sheet name="Schedule E &amp; E-1" sheetId="43" r:id="rId7"/>
     <sheet name="Sch - H" sheetId="10" r:id="rId8"/>
@@ -7673,7 +7674,7 @@
     </row>
     <row r="10" spans="1:34" customFormat="1" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="555" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:34" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -22015,8 +22016,10 @@
       <c r="Y24" s="39"/>
     </row>
     <row r="25" spans="1:25" ht="13" x14ac:dyDescent="0.3">
-      <c r="A25" s="373" t="s">
-        <v>215</v>
+      <c r="A25" s="373" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B25" s="601"/>
       <c r="C25" s="596"/>
@@ -31775,4 +31778,267 @@
     <oddFooter>&amp;C&amp;8&amp;F/&amp;A_x000D_&amp;D_x000D_&amp;T&amp;R&amp;"Arial,Bold"&amp;8Manager:............._x000D_Senior:................_x000D_Staff:..................._x000D__x000D_&amp;12_x000D_D-120HIST</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheetRE.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="62" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <f>'Basic Information'!B4</f>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RETAINED EARNINGS RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Basic Information'!B1</f>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(Amounts in Local Currency and US Dollars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rate @ PY End</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rate @ CY End</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Average rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="F6">
+        <f>'Basic Information'!C61</f>
+      </c>
+      <c r="H6">
+        <f>'Basic Information'!C60</f>
+      </c>
+      <c r="J6">
+        <f>'Basic Information'!C59</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BOY Retained Earnings (prior-year Form 5471, Schedule F line 22)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>'Basic Information'!B2</f>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prior 5471</t>
+        </is>
+      </c>
+      <c r="H10">
+        <f>IF(F10="","",ROUND(F10/$F$6,0))</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net Income (Loss) per books</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="F13">
+        <f>'Income Statement'!F56</f>
+      </c>
+      <c r="H13">
+        <f>ROUND(F13/$J$6,0)</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Increases</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other increase 1</t>
+        </is>
+      </c>
+      <c r="H16">
+        <f>IF(F16="","",ROUND(F16/$H$6,0))</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other increase 2</t>
+        </is>
+      </c>
+      <c r="H17">
+        <f>IF(F17="","",ROUND(F17/$H$6,0))</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Distributions</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dividends</t>
+        </is>
+      </c>
+      <c r="F20">
+        <f>Dividends!C12</f>
+      </c>
+      <c r="H20">
+        <f>Dividends!E12</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="H21">
+        <f>IF(F21="","",ROUND(F21/$H$6,0))</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Decreases / Adjustments</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Translation / other adjustment (confirm — see the re-rollforward exception)</t>
+        </is>
+      </c>
+      <c r="H24">
+        <f>IF(F24="","",ROUND(F24/$H$6,0))</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other decrease 2</t>
+        </is>
+      </c>
+      <c r="H25">
+        <f>IF(F25="","",ROUND(F25/$H$6,0))</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EOY Retained Earnings (computed)</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>'Basic Information'!B1</f>
+      </c>
+      <c r="F27">
+        <f>F10+F13+F16+F17-F20-F21+F24+F25</f>
+      </c>
+      <c r="H27">
+        <f>H10+H13+H16+H17-H20-H21+H24+H25</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EOY Retained Earnings per Schedule F line 22</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>'Balance Sheet'!F61</f>
+      </c>
+      <c r="H28">
+        <f>'Balance Sheet'!H61</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Difference — must be nil before filing</t>
+        </is>
+      </c>
+      <c r="F29">
+        <f>ROUND(F27-F28,2)</f>
+      </c>
+      <c r="H29">
+        <f>ROUND(H27-H28,0)</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>* Enter increases as positive and decreases as negative in column F. Column H translates at the rates on Basic Information: opening at the prior year-end rate, net income at the average rate, everything else at the current year-end rate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>